--- a/real_estate_forms/015_real_estate_incident_report_form--real_estate_forms.xlsx
+++ b/real_estate_forms/015_real_estate_incident_report_form--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -884,8 +884,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -913,12 +913,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'fire'}</t>
+          <t>fire</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Fire'}</t>
+          <t>Fire</t>
         </is>
       </c>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'theft'}</t>
+          <t>theft</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Theft'}</t>
+          <t>Theft</t>
         </is>
       </c>
     </row>
@@ -947,12 +947,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'employee'}</t>
+          <t>employee</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Employee'}</t>
+          <t>Employee</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'public'}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Public'}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'text':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'text': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
